--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.46086520916873</v>
+        <v>3.324890596489919</v>
       </c>
       <c r="D2" t="n">
-        <v>13.72297136877926</v>
+        <v>2.229982847426629</v>
       </c>
       <c r="E2" t="n">
-        <v>8.209661069352983</v>
+        <v>1.334069923769859</v>
       </c>
       <c r="F2" t="n">
-        <v>11.20214380066933</v>
+        <v>1.820348367608766</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.51984714176659</v>
+        <v>4.95947516053707</v>
       </c>
       <c r="D3" t="n">
-        <v>30.81761201293534</v>
+        <v>5.007861952101992</v>
       </c>
       <c r="E3" t="n">
-        <v>8.209661069352983</v>
+        <v>1.334069923769859</v>
       </c>
       <c r="F3" t="n">
-        <v>11.20214380066933</v>
+        <v>1.820348367608766</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.57034519373877</v>
+        <v>6.59268109398255</v>
       </c>
       <c r="D4" t="n">
-        <v>40.85862302329027</v>
+        <v>6.63952624128467</v>
       </c>
       <c r="E4" t="n">
-        <v>8.209661069352983</v>
+        <v>1.334069923769859</v>
       </c>
       <c r="F4" t="n">
-        <v>11.20214380066933</v>
+        <v>1.820348367608766</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
